--- a/fab/GameFive_PickAndPlace.xlsx
+++ b/fab/GameFive_PickAndPlace.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="175">
   <si>
     <t>Designator</t>
   </si>
@@ -127,7 +127,7 @@
     <t>30.48mm</t>
   </si>
   <si>
-    <t>-77.47mm</t>
+    <t>-55.88mm</t>
   </si>
   <si>
     <t>30.06mm</t>
@@ -184,13 +184,13 @@
     <t>CONN-TH_2P-P2.00_KINGHELM_KH-PH-2P-W</t>
   </si>
   <si>
-    <t>35.56mm</t>
-  </si>
-  <si>
-    <t>-80.772mm</t>
-  </si>
-  <si>
-    <t>34.56mm</t>
+    <t>48.26mm</t>
+  </si>
+  <si>
+    <t>-54.61mm</t>
+  </si>
+  <si>
+    <t>47.26mm</t>
   </si>
   <si>
     <t>No</t>
@@ -208,10 +208,13 @@
     <t>83.82mm</t>
   </si>
   <si>
+    <t>-53.34mm</t>
+  </si>
+  <si>
     <t>84.995mm</t>
   </si>
   <si>
-    <t>-78.47mm</t>
+    <t>-54.34mm</t>
   </si>
   <si>
     <t>J3</t>
@@ -226,13 +229,16 @@
     <t>59.995mm</t>
   </si>
   <si>
-    <t>-19.05mm</t>
+    <t>-5.385mm</t>
   </si>
   <si>
     <t>57.245mm</t>
   </si>
   <si>
-    <t>-20.338mm</t>
+    <t>-4.097mm</t>
+  </si>
+  <si>
+    <t>T</t>
   </si>
   <si>
     <t>Q1</t>
@@ -274,6 +280,9 @@
     <t>37.667mm</t>
   </si>
   <si>
+    <t>ERJ2RKF1002X</t>
+  </si>
+  <si>
     <t>R2</t>
   </si>
   <si>
@@ -286,9 +295,6 @@
     <t>R3</t>
   </si>
   <si>
-    <t>48.26mm</t>
-  </si>
-  <si>
     <t>47.827mm</t>
   </si>
   <si>
@@ -442,25 +448,22 @@
     <t>17.043mm</t>
   </si>
   <si>
-    <t>-33.02mm</t>
+    <t>-19.837mm</t>
   </si>
   <si>
     <t>14.793mm</t>
   </si>
   <si>
-    <t>-28.57mm</t>
-  </si>
-  <si>
-    <t>T</t>
+    <t>-15.387mm</t>
   </si>
   <si>
     <t>SW2</t>
   </si>
   <si>
-    <t>-53.34mm</t>
-  </si>
-  <si>
-    <t>-48.89mm</t>
+    <t>-40.157mm</t>
+  </si>
+  <si>
+    <t>-35.707mm</t>
   </si>
   <si>
     <t>SW3</t>
@@ -469,13 +472,13 @@
     <t>6.883mm</t>
   </si>
   <si>
-    <t>-43.18mm</t>
+    <t>-29.997mm</t>
   </si>
   <si>
     <t>4.633mm</t>
   </si>
   <si>
-    <t>-38.73mm</t>
+    <t>-25.547mm</t>
   </si>
   <si>
     <t>SW4</t>
@@ -493,9 +496,15 @@
     <t>111.709mm</t>
   </si>
   <si>
+    <t>-26.187mm</t>
+  </si>
+  <si>
     <t>109.459mm</t>
   </si>
   <si>
+    <t>-21.737mm</t>
+  </si>
+  <si>
     <t>SW6</t>
   </si>
   <si>
@@ -508,28 +517,25 @@
     <t>SW7</t>
   </si>
   <si>
-    <t>GT-TC155C-H0060-L50</t>
-  </si>
-  <si>
-    <t>SW-SMD_4P-G-SWITCH-GT-TC155C-H0060-L50</t>
-  </si>
-  <si>
-    <t>67.564mm</t>
-  </si>
-  <si>
-    <t>64.564mm</t>
-  </si>
-  <si>
-    <t>-74.97mm</t>
+    <t>TS-1187A-B-A-B</t>
+  </si>
+  <si>
+    <t>SW-SMD_4P-L5.1-W5.1-P3.70-LS6.5-TL_H1.5</t>
+  </si>
+  <si>
+    <t>-44.45mm</t>
+  </si>
+  <si>
+    <t>108.709mm</t>
+  </si>
+  <si>
+    <t>-42.575mm</t>
   </si>
   <si>
     <t>SW8</t>
   </si>
   <si>
-    <t>52.324mm</t>
-  </si>
-  <si>
-    <t>49.324mm</t>
+    <t>91.183mm</t>
   </si>
 </sst>
 </file>
@@ -1486,19 +1492,19 @@
         <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="F11" t="s">
         <v>64</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="H11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -1530,37 +1536,37 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" t="s">
         <v>71</v>
       </c>
-      <c r="F12" t="s">
-        <v>70</v>
-      </c>
       <c r="G12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J12">
         <v>14</v>
       </c>
       <c r="K12" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1569,7 +1575,7 @@
         <v>25</v>
       </c>
       <c r="N12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O12" t="s">
         <v>26</v>
@@ -1586,31 +1592,31 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J13">
         <v>3</v>
@@ -1625,7 +1631,7 @@
         <v>25</v>
       </c>
       <c r="N13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O13" t="s">
         <v>26</v>
@@ -1642,31 +1648,31 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J14">
         <v>2</v>
@@ -1681,7 +1687,7 @@
         <v>25</v>
       </c>
       <c r="N14" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="O14" t="s">
         <v>26</v>
@@ -1698,31 +1704,31 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" t="s">
         <v>87</v>
       </c>
-      <c r="B15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E15" t="s">
-        <v>85</v>
-      </c>
       <c r="F15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J15">
         <v>2</v>
@@ -1737,7 +1743,7 @@
         <v>25</v>
       </c>
       <c r="N15" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="O15" t="s">
         <v>26</v>
@@ -1754,31 +1760,31 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="E16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F16" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="G16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J16">
         <v>2</v>
@@ -1793,7 +1799,7 @@
         <v>25</v>
       </c>
       <c r="N16" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="O16" t="s">
         <v>26</v>
@@ -1810,31 +1816,31 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
         <v>30</v>
       </c>
       <c r="E17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F17" t="s">
         <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J17">
         <v>2</v>
@@ -1849,7 +1855,7 @@
         <v>25</v>
       </c>
       <c r="N17" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="O17" t="s">
         <v>26</v>
@@ -1866,31 +1872,31 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F18" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J18">
         <v>2</v>
@@ -1905,7 +1911,7 @@
         <v>25</v>
       </c>
       <c r="N18" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="O18" t="s">
         <v>26</v>
@@ -1922,31 +1928,31 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H19" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J19">
         <v>2</v>
@@ -1961,7 +1967,7 @@
         <v>25</v>
       </c>
       <c r="N19" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="O19" t="s">
         <v>26</v>
@@ -1978,31 +1984,31 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D20" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F20" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I20" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J20">
         <v>2</v>
@@ -2017,7 +2023,7 @@
         <v>25</v>
       </c>
       <c r="N20" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="O20" t="s">
         <v>26</v>
@@ -2034,31 +2040,31 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
         <v>41</v>
       </c>
       <c r="E21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F21" t="s">
         <v>41</v>
       </c>
       <c r="G21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J21">
         <v>2</v>
@@ -2073,7 +2079,7 @@
         <v>25</v>
       </c>
       <c r="N21" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="O21" t="s">
         <v>26</v>
@@ -2090,31 +2096,31 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D22" t="s">
         <v>49</v>
       </c>
       <c r="E22" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F22" t="s">
         <v>49</v>
       </c>
       <c r="G22" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I22" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J22">
         <v>2</v>
@@ -2129,7 +2135,7 @@
         <v>25</v>
       </c>
       <c r="N22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="O22" t="s">
         <v>26</v>
@@ -2146,28 +2152,28 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E23" t="s">
         <v>31</v>
       </c>
       <c r="F23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s">
         <v>31</v>
       </c>
       <c r="H23" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I23" t="s">
         <v>31</v>
@@ -2185,7 +2191,7 @@
         <v>25</v>
       </c>
       <c r="N23" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O23" t="s">
         <v>26</v>
@@ -2202,28 +2208,28 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E24" t="s">
         <v>31</v>
       </c>
       <c r="F24" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G24" t="s">
         <v>31</v>
       </c>
       <c r="H24" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I24" t="s">
         <v>31</v>
@@ -2241,7 +2247,7 @@
         <v>25</v>
       </c>
       <c r="N24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O24" t="s">
         <v>26</v>
@@ -2258,28 +2264,28 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B25" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C25" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E25" t="s">
         <v>22</v>
       </c>
       <c r="F25" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G25" t="s">
         <v>22</v>
       </c>
       <c r="H25" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I25" t="s">
         <v>22</v>
@@ -2297,7 +2303,7 @@
         <v>25</v>
       </c>
       <c r="N25" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O25" t="s">
         <v>26</v>
@@ -2314,31 +2320,31 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B26" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D26" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E26" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F26" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G26" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H26" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I26" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J26">
         <v>25</v>
@@ -2353,7 +2359,7 @@
         <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O26" t="s">
         <v>26</v>
@@ -2370,31 +2376,31 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B27" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D27" t="s">
         <v>21</v>
       </c>
       <c r="E27" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F27" t="s">
         <v>21</v>
       </c>
       <c r="G27" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H27" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I27" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J27">
         <v>16</v>
@@ -2409,7 +2415,7 @@
         <v>25</v>
       </c>
       <c r="N27" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O27" t="s">
         <v>26</v>
@@ -2426,31 +2432,31 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B28" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D28" t="s">
         <v>41</v>
       </c>
       <c r="E28" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F28" t="s">
         <v>41</v>
       </c>
       <c r="G28" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H28" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J28">
         <v>17</v>
@@ -2465,7 +2471,7 @@
         <v>25</v>
       </c>
       <c r="N28" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O28" t="s">
         <v>26</v>
@@ -2482,37 +2488,37 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B29" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C29" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E29" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F29" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G29" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H29" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I29" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J29">
         <v>4</v>
       </c>
       <c r="K29" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -2521,7 +2527,7 @@
         <v>25</v>
       </c>
       <c r="N29" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O29" t="s">
         <v>26</v>
@@ -2538,37 +2544,37 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B30" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C30" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D30" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E30" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F30" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G30" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H30" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I30" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J30">
         <v>4</v>
       </c>
       <c r="K30" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -2577,7 +2583,7 @@
         <v>25</v>
       </c>
       <c r="N30" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O30" t="s">
         <v>26</v>
@@ -2594,37 +2600,37 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B31" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D31" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E31" t="s">
+        <v>153</v>
+      </c>
+      <c r="F31" t="s">
         <v>152</v>
       </c>
-      <c r="F31" t="s">
-        <v>151</v>
-      </c>
       <c r="G31" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H31" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I31" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J31">
         <v>4</v>
       </c>
       <c r="K31" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -2633,7 +2639,7 @@
         <v>25</v>
       </c>
       <c r="N31" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O31" t="s">
         <v>26</v>
@@ -2650,37 +2656,37 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>156</v>
+      </c>
+      <c r="B32" t="s">
+        <v>142</v>
+      </c>
+      <c r="C32" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" t="s">
+        <v>157</v>
+      </c>
+      <c r="E32" t="s">
+        <v>153</v>
+      </c>
+      <c r="F32" t="s">
+        <v>157</v>
+      </c>
+      <c r="G32" t="s">
+        <v>153</v>
+      </c>
+      <c r="H32" t="s">
+        <v>158</v>
+      </c>
+      <c r="I32" t="s">
         <v>155</v>
-      </c>
-      <c r="B32" t="s">
-        <v>140</v>
-      </c>
-      <c r="C32" t="s">
-        <v>141</v>
-      </c>
-      <c r="D32" t="s">
-        <v>156</v>
-      </c>
-      <c r="E32" t="s">
-        <v>152</v>
-      </c>
-      <c r="F32" t="s">
-        <v>156</v>
-      </c>
-      <c r="G32" t="s">
-        <v>152</v>
-      </c>
-      <c r="H32" t="s">
-        <v>157</v>
-      </c>
-      <c r="I32" t="s">
-        <v>154</v>
       </c>
       <c r="J32">
         <v>4</v>
       </c>
       <c r="K32" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -2689,7 +2695,7 @@
         <v>25</v>
       </c>
       <c r="N32" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O32" t="s">
         <v>26</v>
@@ -2706,37 +2712,37 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D33" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E33" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="F33" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G33" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="H33" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="I33" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="J33">
         <v>4</v>
       </c>
       <c r="K33" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -2745,7 +2751,7 @@
         <v>25</v>
       </c>
       <c r="N33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O33" t="s">
         <v>26</v>
@@ -2762,37 +2768,37 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>164</v>
+      </c>
+      <c r="B34" t="s">
+        <v>142</v>
+      </c>
+      <c r="C34" t="s">
+        <v>143</v>
+      </c>
+      <c r="D34" t="s">
+        <v>165</v>
+      </c>
+      <c r="E34" t="s">
         <v>161</v>
       </c>
-      <c r="B34" t="s">
-        <v>140</v>
-      </c>
-      <c r="C34" t="s">
-        <v>141</v>
-      </c>
-      <c r="D34" t="s">
-        <v>162</v>
-      </c>
-      <c r="E34" t="s">
-        <v>152</v>
-      </c>
       <c r="F34" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G34" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="H34" t="s">
+        <v>166</v>
+      </c>
+      <c r="I34" t="s">
         <v>163</v>
-      </c>
-      <c r="I34" t="s">
-        <v>154</v>
       </c>
       <c r="J34">
         <v>4</v>
       </c>
       <c r="K34" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -2801,7 +2807,7 @@
         <v>25</v>
       </c>
       <c r="N34" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O34" t="s">
         <v>26</v>
@@ -2818,37 +2824,37 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B35" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C35" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D35" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E35" t="s">
-        <v>38</v>
+        <v>170</v>
       </c>
       <c r="F35" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="G35" t="s">
-        <v>38</v>
+        <v>170</v>
       </c>
       <c r="H35" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I35" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="J35">
         <v>4</v>
       </c>
       <c r="K35" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -2857,7 +2863,7 @@
         <v>25</v>
       </c>
       <c r="N35" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="O35" t="s">
         <v>26</v>
@@ -2874,37 +2880,37 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>173</v>
+      </c>
+      <c r="B36" t="s">
+        <v>168</v>
+      </c>
+      <c r="C36" t="s">
+        <v>169</v>
+      </c>
+      <c r="D36" t="s">
+        <v>165</v>
+      </c>
+      <c r="E36" t="s">
         <v>170</v>
       </c>
-      <c r="B36" t="s">
+      <c r="F36" t="s">
         <v>165</v>
       </c>
-      <c r="C36" t="s">
-        <v>166</v>
-      </c>
-      <c r="D36" t="s">
-        <v>171</v>
-      </c>
-      <c r="E36" t="s">
-        <v>38</v>
-      </c>
-      <c r="F36" t="s">
-        <v>171</v>
-      </c>
       <c r="G36" t="s">
-        <v>38</v>
+        <v>170</v>
       </c>
       <c r="H36" t="s">
+        <v>174</v>
+      </c>
+      <c r="I36" t="s">
         <v>172</v>
-      </c>
-      <c r="I36" t="s">
-        <v>169</v>
       </c>
       <c r="J36">
         <v>4</v>
       </c>
       <c r="K36" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -2913,7 +2919,7 @@
         <v>25</v>
       </c>
       <c r="N36" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="O36" t="s">
         <v>26</v>

--- a/fab/GameFive_PickAndPlace.xlsx
+++ b/fab/GameFive_PickAndPlace.xlsx
@@ -229,13 +229,13 @@
     <t>59.995mm</t>
   </si>
   <si>
-    <t>-5.385mm</t>
-  </si>
-  <si>
-    <t>57.245mm</t>
-  </si>
-  <si>
-    <t>-4.097mm</t>
+    <t>-17.018mm</t>
+  </si>
+  <si>
+    <t>62.745mm</t>
+  </si>
+  <si>
+    <t>-18.306mm</t>
   </si>
   <si>
     <t>T</t>
@@ -496,13 +496,13 @@
     <t>111.709mm</t>
   </si>
   <si>
-    <t>-26.187mm</t>
+    <t>-31.75mm</t>
   </si>
   <si>
     <t>109.459mm</t>
   </si>
   <si>
-    <t>-21.737mm</t>
+    <t>-27.3mm</t>
   </si>
   <si>
     <t>SW6</t>
@@ -523,13 +523,13 @@
     <t>SW-SMD_4P-L5.1-W5.1-P3.70-LS6.5-TL_H1.5</t>
   </si>
   <si>
-    <t>-44.45mm</t>
+    <t>-17.78mm</t>
   </si>
   <si>
     <t>108.709mm</t>
   </si>
   <si>
-    <t>-42.575mm</t>
+    <t>-15.905mm</t>
   </si>
   <si>
     <t>SW8</t>
@@ -1569,7 +1569,7 @@
         <v>75</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M12" t="s">
         <v>25</v>

--- a/fab/GameFive_PickAndPlace.xlsx
+++ b/fab/GameFive_PickAndPlace.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="160">
   <si>
     <t>Designator</t>
   </si>
@@ -196,27 +196,6 @@
     <t>No</t>
   </si>
   <si>
-    <t>J2</t>
-  </si>
-  <si>
-    <t>PH-2PS</t>
-  </si>
-  <si>
-    <t>CONN-SMD_2P-P2.00_DEALON_PH-2PS</t>
-  </si>
-  <si>
-    <t>83.82mm</t>
-  </si>
-  <si>
-    <t>-53.34mm</t>
-  </si>
-  <si>
-    <t>84.995mm</t>
-  </si>
-  <si>
-    <t>-54.34mm</t>
-  </si>
-  <si>
     <t>J3</t>
   </si>
   <si>
@@ -229,13 +208,13 @@
     <t>59.995mm</t>
   </si>
   <si>
-    <t>-17.018mm</t>
+    <t>-22.098mm</t>
   </si>
   <si>
     <t>62.745mm</t>
   </si>
   <si>
-    <t>-18.306mm</t>
+    <t>-23.386mm</t>
   </si>
   <si>
     <t>T</t>
@@ -370,15 +349,6 @@
     <t>92.277mm</t>
   </si>
   <si>
-    <t>R12</t>
-  </si>
-  <si>
-    <t>67.31mm</t>
-  </si>
-  <si>
-    <t>66.877mm</t>
-  </si>
-  <si>
     <t>U1</t>
   </si>
   <si>
@@ -419,21 +389,6 @@
   </si>
   <si>
     <t>-37.768mm</t>
-  </si>
-  <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>MAX98357AETE+T</t>
-  </si>
-  <si>
-    <t>TQFN-16_L3.0-W3.0-P0.50-BL-EP1.5</t>
-  </si>
-  <si>
-    <t>72.912mm</t>
-  </si>
-  <si>
-    <t>-39.14mm</t>
   </si>
   <si>
     <t>SW1</t>
@@ -912,7 +867,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="18" width="20" customWidth="1"/>
@@ -1507,13 +1462,13 @@
         <v>67</v>
       </c>
       <c r="J11">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K11" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L11">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M11" t="s">
         <v>25</v>
@@ -1536,46 +1491,46 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" t="s">
+        <v>74</v>
+      </c>
+      <c r="I12" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12">
+        <v>3</v>
+      </c>
+      <c r="K12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N12" t="s">
         <v>70</v>
-      </c>
-      <c r="D12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12" t="s">
-        <v>72</v>
-      </c>
-      <c r="F12" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12" t="s">
-        <v>72</v>
-      </c>
-      <c r="H12" t="s">
-        <v>73</v>
-      </c>
-      <c r="I12" t="s">
-        <v>74</v>
-      </c>
-      <c r="J12">
-        <v>14</v>
-      </c>
-      <c r="K12" t="s">
-        <v>75</v>
-      </c>
-      <c r="L12">
-        <v>180</v>
-      </c>
-      <c r="M12" t="s">
-        <v>25</v>
-      </c>
-      <c r="N12" t="s">
-        <v>69</v>
       </c>
       <c r="O12" t="s">
         <v>26</v>
@@ -1616,10 +1571,10 @@
         <v>81</v>
       </c>
       <c r="I13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K13" t="s">
         <v>24</v>
@@ -1631,7 +1586,7 @@
         <v>25</v>
       </c>
       <c r="N13" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="O13" t="s">
         <v>26</v>
@@ -1651,28 +1606,28 @@
         <v>83</v>
       </c>
       <c r="B14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" t="s">
         <v>84</v>
       </c>
-      <c r="C14" t="s">
+      <c r="E14" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" t="s">
         <v>85</v>
       </c>
-      <c r="D14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" t="s">
-        <v>87</v>
-      </c>
-      <c r="F14" t="s">
-        <v>86</v>
-      </c>
-      <c r="G14" t="s">
-        <v>87</v>
-      </c>
-      <c r="H14" t="s">
-        <v>88</v>
-      </c>
       <c r="I14" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J14">
         <v>2</v>
@@ -1687,7 +1642,7 @@
         <v>25</v>
       </c>
       <c r="N14" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="O14" t="s">
         <v>26</v>
@@ -1704,31 +1659,31 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15" t="s">
         <v>87</v>
       </c>
-      <c r="F15" t="s">
-        <v>91</v>
-      </c>
-      <c r="G15" t="s">
-        <v>87</v>
-      </c>
-      <c r="H15" t="s">
-        <v>92</v>
-      </c>
       <c r="I15" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J15">
         <v>2</v>
@@ -1743,7 +1698,7 @@
         <v>25</v>
       </c>
       <c r="N15" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="O15" t="s">
         <v>26</v>
@@ -1760,31 +1715,31 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="E16" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="G16" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I16" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J16">
         <v>2</v>
@@ -1799,7 +1754,7 @@
         <v>25</v>
       </c>
       <c r="N16" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="O16" t="s">
         <v>26</v>
@@ -1816,31 +1771,31 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="G17" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H17" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J17">
         <v>2</v>
@@ -1855,7 +1810,7 @@
         <v>25</v>
       </c>
       <c r="N17" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="O17" t="s">
         <v>26</v>
@@ -1872,31 +1827,31 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E18" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F18" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G18" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I18" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J18">
         <v>2</v>
@@ -1911,7 +1866,7 @@
         <v>25</v>
       </c>
       <c r="N18" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="O18" t="s">
         <v>26</v>
@@ -1928,31 +1883,31 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D19" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E19" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F19" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G19" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I19" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J19">
         <v>2</v>
@@ -1967,7 +1922,7 @@
         <v>25</v>
       </c>
       <c r="N19" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="O19" t="s">
         <v>26</v>
@@ -1984,31 +1939,31 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="E20" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F20" t="s">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="G20" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I20" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J20">
         <v>2</v>
@@ -2023,7 +1978,7 @@
         <v>25</v>
       </c>
       <c r="N20" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="O20" t="s">
         <v>26</v>
@@ -2040,31 +1995,31 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E21" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F21" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G21" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="H21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I21" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="J21">
         <v>2</v>
@@ -2079,7 +2034,7 @@
         <v>25</v>
       </c>
       <c r="N21" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="O21" t="s">
         <v>26</v>
@@ -2096,31 +2051,31 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="F22" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="G22" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="H22" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I22" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="J22">
         <v>2</v>
@@ -2135,7 +2090,7 @@
         <v>25</v>
       </c>
       <c r="N22" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="O22" t="s">
         <v>26</v>
@@ -2152,28 +2107,28 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B23" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="E23" t="s">
         <v>31</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="G23" t="s">
         <v>31</v>
       </c>
       <c r="H23" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I23" t="s">
         <v>31</v>
@@ -2191,7 +2146,7 @@
         <v>25</v>
       </c>
       <c r="N23" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="O23" t="s">
         <v>26</v>
@@ -2208,46 +2163,46 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" t="s">
+        <v>113</v>
+      </c>
+      <c r="C24" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" t="s">
         <v>115</v>
       </c>
-      <c r="B24" t="s">
+      <c r="E24" t="s">
         <v>116</v>
       </c>
-      <c r="C24" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
+        <v>115</v>
+      </c>
+      <c r="G24" t="s">
+        <v>116</v>
+      </c>
+      <c r="H24" t="s">
         <v>117</v>
       </c>
-      <c r="E24" t="s">
-        <v>31</v>
-      </c>
-      <c r="F24" t="s">
-        <v>117</v>
-      </c>
-      <c r="G24" t="s">
-        <v>31</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>118</v>
       </c>
-      <c r="I24" t="s">
-        <v>31</v>
-      </c>
       <c r="J24">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K24" t="s">
         <v>24</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M24" t="s">
         <v>25</v>
       </c>
       <c r="N24" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="O24" t="s">
         <v>26</v>
@@ -2264,34 +2219,34 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B25" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="D25" t="s">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="E25" t="s">
-        <v>22</v>
+        <v>123</v>
       </c>
       <c r="F25" t="s">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="G25" t="s">
-        <v>22</v>
+        <v>123</v>
       </c>
       <c r="H25" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I25" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K25" t="s">
         <v>24</v>
@@ -2303,7 +2258,7 @@
         <v>25</v>
       </c>
       <c r="N25" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="O25" t="s">
         <v>26</v>
@@ -2320,46 +2275,46 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C26" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D26" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E26" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F26" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G26" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H26" t="s">
+        <v>131</v>
+      </c>
+      <c r="I26" t="s">
+        <v>132</v>
+      </c>
+      <c r="J26">
+        <v>4</v>
+      </c>
+      <c r="K26" t="s">
+        <v>68</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="s">
+        <v>25</v>
+      </c>
+      <c r="N26" t="s">
         <v>127</v>
-      </c>
-      <c r="I26" t="s">
-        <v>128</v>
-      </c>
-      <c r="J26">
-        <v>25</v>
-      </c>
-      <c r="K26" t="s">
-        <v>24</v>
-      </c>
-      <c r="L26">
-        <v>90</v>
-      </c>
-      <c r="M26" t="s">
-        <v>25</v>
-      </c>
-      <c r="N26" t="s">
-        <v>129</v>
       </c>
       <c r="O26" t="s">
         <v>26</v>
@@ -2376,37 +2331,37 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B27" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" t="s">
+        <v>129</v>
+      </c>
+      <c r="E27" t="s">
+        <v>134</v>
+      </c>
+      <c r="F27" t="s">
+        <v>129</v>
+      </c>
+      <c r="G27" t="s">
+        <v>134</v>
+      </c>
+      <c r="H27" t="s">
         <v>131</v>
-      </c>
-      <c r="C27" t="s">
-        <v>132</v>
-      </c>
-      <c r="D27" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F27" t="s">
-        <v>21</v>
-      </c>
-      <c r="G27" t="s">
-        <v>133</v>
-      </c>
-      <c r="H27" t="s">
-        <v>134</v>
       </c>
       <c r="I27" t="s">
         <v>135</v>
       </c>
       <c r="J27">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K27" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -2415,7 +2370,7 @@
         <v>25</v>
       </c>
       <c r="N27" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O27" t="s">
         <v>26</v>
@@ -2435,22 +2390,22 @@
         <v>136</v>
       </c>
       <c r="B28" t="s">
+        <v>127</v>
+      </c>
+      <c r="C28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D28" t="s">
         <v>137</v>
       </c>
-      <c r="C28" t="s">
+      <c r="E28" t="s">
         <v>138</v>
       </c>
-      <c r="D28" t="s">
-        <v>41</v>
-      </c>
-      <c r="E28" t="s">
-        <v>133</v>
-      </c>
       <c r="F28" t="s">
-        <v>41</v>
+        <v>137</v>
       </c>
       <c r="G28" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H28" t="s">
         <v>139</v>
@@ -2459,10 +2414,10 @@
         <v>140</v>
       </c>
       <c r="J28">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="K28" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -2471,7 +2426,7 @@
         <v>25</v>
       </c>
       <c r="N28" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="O28" t="s">
         <v>26</v>
@@ -2491,34 +2446,34 @@
         <v>141</v>
       </c>
       <c r="B29" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" t="s">
         <v>142</v>
       </c>
-      <c r="C29" t="s">
+      <c r="E29" t="s">
+        <v>138</v>
+      </c>
+      <c r="F29" t="s">
+        <v>142</v>
+      </c>
+      <c r="G29" t="s">
+        <v>138</v>
+      </c>
+      <c r="H29" t="s">
         <v>143</v>
       </c>
-      <c r="D29" t="s">
-        <v>144</v>
-      </c>
-      <c r="E29" t="s">
-        <v>145</v>
-      </c>
-      <c r="F29" t="s">
-        <v>144</v>
-      </c>
-      <c r="G29" t="s">
-        <v>145</v>
-      </c>
-      <c r="H29" t="s">
-        <v>146</v>
-      </c>
       <c r="I29" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="J29">
         <v>4</v>
       </c>
       <c r="K29" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -2527,7 +2482,7 @@
         <v>25</v>
       </c>
       <c r="N29" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="O29" t="s">
         <v>26</v>
@@ -2544,37 +2499,37 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>144</v>
+      </c>
+      <c r="B30" t="s">
+        <v>127</v>
+      </c>
+      <c r="C30" t="s">
+        <v>128</v>
+      </c>
+      <c r="D30" t="s">
+        <v>145</v>
+      </c>
+      <c r="E30" t="s">
+        <v>146</v>
+      </c>
+      <c r="F30" t="s">
+        <v>145</v>
+      </c>
+      <c r="G30" t="s">
+        <v>146</v>
+      </c>
+      <c r="H30" t="s">
+        <v>147</v>
+      </c>
+      <c r="I30" t="s">
         <v>148</v>
-      </c>
-      <c r="B30" t="s">
-        <v>142</v>
-      </c>
-      <c r="C30" t="s">
-        <v>143</v>
-      </c>
-      <c r="D30" t="s">
-        <v>144</v>
-      </c>
-      <c r="E30" t="s">
-        <v>149</v>
-      </c>
-      <c r="F30" t="s">
-        <v>144</v>
-      </c>
-      <c r="G30" t="s">
-        <v>149</v>
-      </c>
-      <c r="H30" t="s">
-        <v>146</v>
-      </c>
-      <c r="I30" t="s">
-        <v>150</v>
       </c>
       <c r="J30">
         <v>4</v>
       </c>
       <c r="K30" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -2583,7 +2538,7 @@
         <v>25</v>
       </c>
       <c r="N30" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="O30" t="s">
         <v>26</v>
@@ -2600,37 +2555,37 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>149</v>
+      </c>
+      <c r="B31" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D31" t="s">
+        <v>150</v>
+      </c>
+      <c r="E31" t="s">
+        <v>146</v>
+      </c>
+      <c r="F31" t="s">
+        <v>150</v>
+      </c>
+      <c r="G31" t="s">
+        <v>146</v>
+      </c>
+      <c r="H31" t="s">
         <v>151</v>
       </c>
-      <c r="B31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C31" t="s">
-        <v>143</v>
-      </c>
-      <c r="D31" t="s">
-        <v>152</v>
-      </c>
-      <c r="E31" t="s">
-        <v>153</v>
-      </c>
-      <c r="F31" t="s">
-        <v>152</v>
-      </c>
-      <c r="G31" t="s">
-        <v>153</v>
-      </c>
-      <c r="H31" t="s">
-        <v>154</v>
-      </c>
       <c r="I31" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="J31">
         <v>4</v>
       </c>
       <c r="K31" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -2639,7 +2594,7 @@
         <v>25</v>
       </c>
       <c r="N31" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="O31" t="s">
         <v>26</v>
@@ -2656,37 +2611,37 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>152</v>
+      </c>
+      <c r="B32" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32" t="s">
+        <v>154</v>
+      </c>
+      <c r="D32" t="s">
+        <v>145</v>
+      </c>
+      <c r="E32" t="s">
+        <v>155</v>
+      </c>
+      <c r="F32" t="s">
+        <v>145</v>
+      </c>
+      <c r="G32" t="s">
+        <v>155</v>
+      </c>
+      <c r="H32" t="s">
         <v>156</v>
       </c>
-      <c r="B32" t="s">
-        <v>142</v>
-      </c>
-      <c r="C32" t="s">
-        <v>143</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="I32" t="s">
         <v>157</v>
-      </c>
-      <c r="E32" t="s">
-        <v>153</v>
-      </c>
-      <c r="F32" t="s">
-        <v>157</v>
-      </c>
-      <c r="G32" t="s">
-        <v>153</v>
-      </c>
-      <c r="H32" t="s">
-        <v>158</v>
-      </c>
-      <c r="I32" t="s">
-        <v>155</v>
       </c>
       <c r="J32">
         <v>4</v>
       </c>
       <c r="K32" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -2695,7 +2650,7 @@
         <v>25</v>
       </c>
       <c r="N32" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="O32" t="s">
         <v>26</v>
@@ -2712,37 +2667,37 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>158</v>
+      </c>
+      <c r="B33" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" t="s">
+        <v>154</v>
+      </c>
+      <c r="D33" t="s">
+        <v>150</v>
+      </c>
+      <c r="E33" t="s">
+        <v>155</v>
+      </c>
+      <c r="F33" t="s">
+        <v>150</v>
+      </c>
+      <c r="G33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H33" t="s">
         <v>159</v>
       </c>
-      <c r="B33" t="s">
-        <v>142</v>
-      </c>
-      <c r="C33" t="s">
-        <v>143</v>
-      </c>
-      <c r="D33" t="s">
-        <v>160</v>
-      </c>
-      <c r="E33" t="s">
-        <v>161</v>
-      </c>
-      <c r="F33" t="s">
-        <v>160</v>
-      </c>
-      <c r="G33" t="s">
-        <v>161</v>
-      </c>
-      <c r="H33" t="s">
-        <v>162</v>
-      </c>
       <c r="I33" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="J33">
         <v>4</v>
       </c>
       <c r="K33" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -2751,7 +2706,7 @@
         <v>25</v>
       </c>
       <c r="N33" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="O33" t="s">
         <v>26</v>
@@ -2763,174 +2718,6 @@
         <v>27</v>
       </c>
       <c r="R33" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>164</v>
-      </c>
-      <c r="B34" t="s">
-        <v>142</v>
-      </c>
-      <c r="C34" t="s">
-        <v>143</v>
-      </c>
-      <c r="D34" t="s">
-        <v>165</v>
-      </c>
-      <c r="E34" t="s">
-        <v>161</v>
-      </c>
-      <c r="F34" t="s">
-        <v>165</v>
-      </c>
-      <c r="G34" t="s">
-        <v>161</v>
-      </c>
-      <c r="H34" t="s">
-        <v>166</v>
-      </c>
-      <c r="I34" t="s">
-        <v>163</v>
-      </c>
-      <c r="J34">
-        <v>4</v>
-      </c>
-      <c r="K34" t="s">
-        <v>75</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34" t="s">
-        <v>25</v>
-      </c>
-      <c r="N34" t="s">
-        <v>142</v>
-      </c>
-      <c r="O34" t="s">
-        <v>26</v>
-      </c>
-      <c r="P34" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>27</v>
-      </c>
-      <c r="R34" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>167</v>
-      </c>
-      <c r="B35" t="s">
-        <v>168</v>
-      </c>
-      <c r="C35" t="s">
-        <v>169</v>
-      </c>
-      <c r="D35" t="s">
-        <v>160</v>
-      </c>
-      <c r="E35" t="s">
-        <v>170</v>
-      </c>
-      <c r="F35" t="s">
-        <v>160</v>
-      </c>
-      <c r="G35" t="s">
-        <v>170</v>
-      </c>
-      <c r="H35" t="s">
-        <v>171</v>
-      </c>
-      <c r="I35" t="s">
-        <v>172</v>
-      </c>
-      <c r="J35">
-        <v>4</v>
-      </c>
-      <c r="K35" t="s">
-        <v>75</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35" t="s">
-        <v>25</v>
-      </c>
-      <c r="N35" t="s">
-        <v>168</v>
-      </c>
-      <c r="O35" t="s">
-        <v>26</v>
-      </c>
-      <c r="P35" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>27</v>
-      </c>
-      <c r="R35" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>173</v>
-      </c>
-      <c r="B36" t="s">
-        <v>168</v>
-      </c>
-      <c r="C36" t="s">
-        <v>169</v>
-      </c>
-      <c r="D36" t="s">
-        <v>165</v>
-      </c>
-      <c r="E36" t="s">
-        <v>170</v>
-      </c>
-      <c r="F36" t="s">
-        <v>165</v>
-      </c>
-      <c r="G36" t="s">
-        <v>170</v>
-      </c>
-      <c r="H36" t="s">
-        <v>174</v>
-      </c>
-      <c r="I36" t="s">
-        <v>172</v>
-      </c>
-      <c r="J36">
-        <v>4</v>
-      </c>
-      <c r="K36" t="s">
-        <v>75</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36" t="s">
-        <v>25</v>
-      </c>
-      <c r="N36" t="s">
-        <v>168</v>
-      </c>
-      <c r="O36" t="s">
-        <v>26</v>
-      </c>
-      <c r="P36" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>27</v>
-      </c>
-      <c r="R36" t="s">
         <v>26</v>
       </c>
     </row>

--- a/fab/GameFive_PickAndPlace.xlsx
+++ b/fab/GameFive_PickAndPlace.xlsx
@@ -208,13 +208,13 @@
     <t>59.995mm</t>
   </si>
   <si>
-    <t>-22.098mm</t>
+    <t>-21.361mm</t>
   </si>
   <si>
     <t>62.745mm</t>
   </si>
   <si>
-    <t>-23.386mm</t>
+    <t>-22.649mm</t>
   </si>
   <si>
     <t>T</t>

--- a/fab/GameFive_PickAndPlace.xlsx
+++ b/fab/GameFive_PickAndPlace.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="162">
   <si>
     <t>Designator</t>
   </si>
@@ -451,13 +451,13 @@
     <t>111.709mm</t>
   </si>
   <si>
-    <t>-31.75mm</t>
+    <t>-36.83mm</t>
   </si>
   <si>
     <t>109.459mm</t>
   </si>
   <si>
-    <t>-27.3mm</t>
+    <t>-32.38mm</t>
   </si>
   <si>
     <t>SW6</t>
@@ -472,25 +472,31 @@
     <t>SW7</t>
   </si>
   <si>
-    <t>TS-1187A-B-A-B</t>
-  </si>
-  <si>
-    <t>SW-SMD_4P-L5.1-W5.1-P3.70-LS6.5-TL_H1.5</t>
-  </si>
-  <si>
-    <t>-17.78mm</t>
-  </si>
-  <si>
-    <t>108.709mm</t>
-  </si>
-  <si>
-    <t>-15.905mm</t>
+    <t>TS-1187A-C-H-B</t>
+  </si>
+  <si>
+    <t>SW-SMD_4P-L5.1-W5.1-P3.70-LS6.5-TL_H4.0</t>
+  </si>
+  <si>
+    <t>67.615mm</t>
+  </si>
+  <si>
+    <t>-57.912mm</t>
+  </si>
+  <si>
+    <t>64.315mm</t>
+  </si>
+  <si>
+    <t>-56.062mm</t>
   </si>
   <si>
     <t>SW8</t>
   </si>
   <si>
-    <t>91.183mm</t>
+    <t>52.375mm</t>
+  </si>
+  <si>
+    <t>49.075mm</t>
   </si>
 </sst>
 </file>
@@ -2620,22 +2626,22 @@
         <v>154</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="E32" t="s">
+        <v>156</v>
+      </c>
+      <c r="F32" t="s">
         <v>155</v>
       </c>
-      <c r="F32" t="s">
-        <v>145</v>
-      </c>
       <c r="G32" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H32" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I32" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J32">
         <v>4</v>
@@ -2667,7 +2673,7 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B33" t="s">
         <v>153</v>
@@ -2676,22 +2682,22 @@
         <v>154</v>
       </c>
       <c r="D33" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F33" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J33">
         <v>4</v>

--- a/fab/GameFive_PickAndPlace.xlsx
+++ b/fab/GameFive_PickAndPlace.xlsx
@@ -184,96 +184,96 @@
     <t>CONN-TH_2P-P2.00_KINGHELM_KH-PH-2P-W</t>
   </si>
   <si>
+    <t>43.18mm</t>
+  </si>
+  <si>
+    <t>-50.8mm</t>
+  </si>
+  <si>
+    <t>42.18mm</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>J3</t>
+  </si>
+  <si>
+    <t>X05A20L12T</t>
+  </si>
+  <si>
+    <t>FFC-SMD_12P-P0.50_X05A20L12T</t>
+  </si>
+  <si>
+    <t>59.995mm</t>
+  </si>
+  <si>
+    <t>-14.732mm</t>
+  </si>
+  <si>
+    <t>62.745mm</t>
+  </si>
+  <si>
+    <t>-16.02mm</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>SI2302</t>
+  </si>
+  <si>
+    <t>SOT-23_L2.9-W1.3-P1.90-LS2.4-BR</t>
+  </si>
+  <si>
+    <t>86.36mm</t>
+  </si>
+  <si>
+    <t>-20.32mm</t>
+  </si>
+  <si>
+    <t>87.51mm</t>
+  </si>
+  <si>
+    <t>-19.37mm</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>0402WGF1002TCE</t>
+  </si>
+  <si>
+    <t>R0402</t>
+  </si>
+  <si>
+    <t>38.1mm</t>
+  </si>
+  <si>
+    <t>-52.07mm</t>
+  </si>
+  <si>
+    <t>37.667mm</t>
+  </si>
+  <si>
+    <t>ERJ2RKF1002X</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>42.747mm</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
     <t>48.26mm</t>
   </si>
   <si>
-    <t>-54.61mm</t>
-  </si>
-  <si>
-    <t>47.26mm</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>J3</t>
-  </si>
-  <si>
-    <t>X05A20L12T</t>
-  </si>
-  <si>
-    <t>FFC-SMD_12P-P0.50_X05A20L12T</t>
-  </si>
-  <si>
-    <t>59.995mm</t>
-  </si>
-  <si>
-    <t>-21.361mm</t>
-  </si>
-  <si>
-    <t>62.745mm</t>
-  </si>
-  <si>
-    <t>-22.649mm</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>SI2302</t>
-  </si>
-  <si>
-    <t>SOT-23_L2.9-W1.3-P1.90-LS2.4-BR</t>
-  </si>
-  <si>
-    <t>86.36mm</t>
-  </si>
-  <si>
-    <t>-20.32mm</t>
-  </si>
-  <si>
-    <t>87.51mm</t>
-  </si>
-  <si>
-    <t>-19.37mm</t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>0402WGF1002TCE</t>
-  </si>
-  <si>
-    <t>R0402</t>
-  </si>
-  <si>
-    <t>38.1mm</t>
-  </si>
-  <si>
-    <t>-52.07mm</t>
-  </si>
-  <si>
-    <t>37.667mm</t>
-  </si>
-  <si>
-    <t>ERJ2RKF1002X</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>43.18mm</t>
-  </si>
-  <si>
-    <t>42.747mm</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
     <t>47.827mm</t>
   </si>
   <si>
@@ -361,13 +361,13 @@
     <t>109.347mm</t>
   </si>
   <si>
-    <t>-22.86mm</t>
+    <t>-17.78mm</t>
   </si>
   <si>
     <t>116.459mm</t>
   </si>
   <si>
-    <t>-30.984mm</t>
+    <t>-25.904mm</t>
   </si>
   <si>
     <t>XIAO ESP32S3</t>
@@ -472,22 +472,22 @@
     <t>SW7</t>
   </si>
   <si>
-    <t>TS-1187A-C-H-B</t>
-  </si>
-  <si>
-    <t>SW-SMD_4P-L5.1-W5.1-P3.70-LS6.5-TL_H4.0</t>
+    <t>B3F-1025</t>
+  </si>
+  <si>
+    <t>SW-TH_4P-L6.2-W6.2-P4.50-LS6.5</t>
   </si>
   <si>
     <t>67.615mm</t>
   </si>
   <si>
-    <t>-57.912mm</t>
-  </si>
-  <si>
-    <t>64.315mm</t>
-  </si>
-  <si>
-    <t>-56.062mm</t>
+    <t>-57.277mm</t>
+  </si>
+  <si>
+    <t>64.365mm</t>
+  </si>
+  <si>
+    <t>-55.027mm</t>
   </si>
   <si>
     <t>SW8</t>
@@ -496,7 +496,7 @@
     <t>52.375mm</t>
   </si>
   <si>
-    <t>49.075mm</t>
+    <t>49.125mm</t>
   </si>
 </sst>
 </file>
@@ -1618,19 +1618,19 @@
         <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s">
         <v>80</v>
       </c>
       <c r="F14" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="G14" t="s">
         <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I14" t="s">
         <v>80</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
         <v>77</v>
@@ -1674,13 +1674,13 @@
         <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="E15" t="s">
         <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="G15" t="s">
         <v>80</v>
@@ -2653,7 +2653,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="N32" t="s">
         <v>153</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="N33" t="s">
         <v>153</v>

--- a/fab/GameFive_PickAndPlace.xlsx
+++ b/fab/GameFive_PickAndPlace.xlsx
@@ -205,16 +205,16 @@
     <t>FFC-SMD_12P-P0.50_X05A20L12T</t>
   </si>
   <si>
-    <t>59.995mm</t>
-  </si>
-  <si>
-    <t>-14.732mm</t>
-  </si>
-  <si>
-    <t>62.745mm</t>
-  </si>
-  <si>
-    <t>-16.02mm</t>
+    <t>59.944mm</t>
+  </si>
+  <si>
+    <t>-22.606mm</t>
+  </si>
+  <si>
+    <t>62.694mm</t>
+  </si>
+  <si>
+    <t>-23.894mm</t>
   </si>
   <si>
     <t>T</t>

--- a/fab/GameFive_PickAndPlace.xlsx
+++ b/fab/GameFive_PickAndPlace.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="18"/>
@@ -611,14 +611,11 @@
           <t>CL05B104KO5NNNC</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -687,14 +684,11 @@
           <t>CL05A105KA5NQNC</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -763,14 +757,11 @@
           <t>CL05B104KO5NNNC</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -839,14 +830,11 @@
           <t>CL05A105KA5NQNC</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -915,14 +903,11 @@
           <t>CL05B104KO5NNNC</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -991,14 +976,11 @@
           <t>CL05B104KO5NNNC</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1067,14 +1049,11 @@
           <t>CL10A106KP8NNNC</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1143,14 +1122,11 @@
           <t>CL10A106KP8NNNC</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1219,14 +1195,11 @@
           <t>KH-PH-2P-W</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1295,14 +1268,11 @@
           <t>X05A20L12T</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1371,14 +1341,11 @@
           <t>SI2302</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1447,14 +1414,11 @@
           <t>ERJ2RKF1002X</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1523,14 +1487,11 @@
           <t>ERJ2RKF1002X</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1599,14 +1560,11 @@
           <t>ERJ2RKF1002X</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1675,14 +1633,11 @@
           <t>ERJ2RKF1002X</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1751,14 +1706,11 @@
           <t>ERJ2RKF1002X</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1827,14 +1779,11 @@
           <t>ERJ2RKF1002X</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1903,14 +1852,11 @@
           <t>ERJ2RKF1002X</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1979,14 +1925,11 @@
           <t>ERJ2RKF1002X</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2055,14 +1998,11 @@
           <t>0805W8F220JT5E</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2131,14 +2071,11 @@
           <t>0402WGF1000TCE</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2207,14 +2144,11 @@
           <t>0402WGF1003TCE</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2283,14 +2217,11 @@
           <t>XIAO ESP32S3</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2359,14 +2290,11 @@
           <t>SN74HC165DR</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2435,14 +2363,11 @@
           <t>EVQQ1D06M</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2511,14 +2436,11 @@
           <t>EVQQ1D06M</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2587,14 +2509,11 @@
           <t>EVQQ1D06M</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2663,14 +2582,11 @@
           <t>EVQQ1D06M</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2739,14 +2655,11 @@
           <t>EVQQ1D06M</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2815,14 +2728,11 @@
           <t>EVQQ1D06M</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2891,14 +2801,11 @@
           <t>B3F-1025</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2967,14 +2874,221 @@
           <t>B3F-1025</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MAX98357AETE+T</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>TQFN-16_L3.0-W3.0-P0.50-BL-EP1.5</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>93.98mm</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-46.99mm</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>93.98mm</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-46.99mm</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>93.98mm</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>-46.99mm</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>MAX98357AETE+T</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>LCSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>J2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1.25T-2A</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CONN-TH_1.25T-1-2A</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>104.14mm</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-54.61mm</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>104.14mm</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-54.61mm</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>104.14mm</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>-54.61mm</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>1.25T-2A</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>LCSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0402WGF1003TCE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>R0402</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>87.63mm</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-46.99mm</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>87.63mm</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-46.99mm</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>87.63mm</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>-46.99mm</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0402WGF1003TCE</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>LCSC</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <printOptions gridLines="1"/>
